--- a/generated/spreadsheet/verbose/lawful-development-certficate-proposed-work-to-a-listed-building-ldc-proposed-work-lb-verbose.xlsx
+++ b/generated/spreadsheet/verbose/lawful-development-certficate-proposed-work-to-a-listed-building-ldc-proposed-work-lb-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -440,9 +440,9 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1980,19 +1980,27 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>address-text</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2036,19 +2044,27 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,21 +2098,37 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2130,12 +2162,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -2144,12 +2176,12 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2159,56 +2191,64 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2216,31 +2256,23 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2274,29 +2306,21 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2306,7 +2330,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2340,24 +2364,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -2367,64 +2391,72 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2442,29 +2474,21 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2474,7 +2498,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2508,19 +2532,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2530,7 +2554,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2564,19 +2588,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2620,19 +2644,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2676,95 +2700,155 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
-    </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -2774,74 +2858,62 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Declaration</t>
+          <t>Conflict of interest</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>declaration</t>
+          <t>conflict-of-interest</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>person-reference</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Person reference</t>
-        </is>
-      </c>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2852,12 +2924,12 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -2867,8 +2939,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="2" t="n"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -2876,12 +2956,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2892,12 +2972,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2907,29 +2987,21 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Description of proposed works for listed building lawful development certificate</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>desc-proposed-works-lb-ldc</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Details of development plans for the work to the listed building an applicant is seeking a lawful development certificate for</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Description of Proposed Works</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2940,12 +3012,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>A detailed description of the proposed works (including existing and proposed materials and finishes) together with details of those parts) of the building that are likely to be affected.</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2955,29 +3027,21 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Grounds for application</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>grounds-for-application</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Why a Certificate of Lawfulness of Propose Works is being requested.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>grounds-for-application</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Grounds for application</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2988,14 +3052,12 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reason(s) why Certificate of Lawfulness of Proposed Works should be granted,
-including explanation of why listed building consent is not required
-</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3005,40 +3067,40 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="2" t="n"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Description of proposed works for listed building lawful development certificate</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>desc-proposed-works-lb-ldc</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Why a Certificate of Lawfulness of Propose Works is being requested.</t>
+          <t>Details of development plans for the work to the listed building an applicant is seeking a lawful development certificate for</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Description of Proposed Works</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A detailed description of the proposed works (including existing and proposed materials and finishes) together with details of those parts) of the building that are likely to be affected.</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3055,27 +3117,27 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Interest details</t>
+          <t>Grounds for application</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>interest-details</t>
+          <t>grounds-for-application</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
+          <t>Why a Certificate of Lawfulness of Propose Works is being requested.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>applicant-interest-type</t>
+          <t>grounds-for-application</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest type</t>
+          <t>Grounds for application</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3086,12 +3148,14 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>The applicant’s relationship to the land, property or building</t>
+          <t xml:space="preserve">Reason(s) why Certificate of Lawfulness of Proposed Works should be granted,
+including explanation of why listed building consent is not required
+</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -3105,44 +3169,36 @@
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
+          <t>Why a Certificate of Lawfulness of Propose Works is being requested.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>owner-details</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Owner details[]</t>
+          <t>Supporting documents[]</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3152,13 +3208,21 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n"/>
-      <c r="B52" s="2" t="n"/>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Interest details</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>interest-details</t>
+        </is>
+      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
@@ -3166,44 +3230,28 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>owner-details</t>
+          <t>applicant-interest-type</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Owner details[]</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>first-name</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Applicant interest type</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The applicant’s relationship to the land, property or building</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -3242,19 +3290,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -3264,7 +3312,7 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3298,19 +3346,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -3354,19 +3402,19 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3376,7 +3424,7 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3400,26 +3448,42 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>informed-of-application</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Whether the owner has been informed of the application</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3438,12 +3502,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>interested-persons</t>
+          <t>owner-details</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
+          <t>Owner details[]</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3458,19 +3522,27 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>contact-address</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3494,12 +3566,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>interested-persons</t>
+          <t>owner-details</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
+          <t>Owner details[]</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3514,19 +3586,27 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>contact-address</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3536,7 +3616,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3550,44 +3630,36 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>interested-persons</t>
+          <t>owner-details</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
+          <t>Owner details[]</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>informed-of-application</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>last-name</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
+          <t>Informed of application</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Whether the owner has been informed of the application</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -3626,19 +3698,19 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3648,7 +3720,7 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3682,19 +3754,19 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3704,7 +3776,7 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3728,21 +3800,29 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>nature-of-interest</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Nature of interest</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>last-name</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Last Name</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Description of the nature of a person's interest in the property</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -3776,26 +3856,42 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>informed-of-application</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Whether the person has been informed of the application</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -3824,21 +3920,37 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>reason-not-informed</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Reason not informed</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Reason why a person was not informed of the application</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -3853,50 +3965,66 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Listed building grade</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>lb-grade</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>The grade of any listed building affected by the proposed development.</t>
+          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>listed-building-grade</t>
+          <t>interested-persons</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Listed building grade</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3905,28 +4033,36 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>The grade of any listed building affected by the proposed development.</t>
+          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>listed-building</t>
+          <t>interested-persons</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Listed building</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>nature-of-interest</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Nature of interest</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Listed building reference for cross-referencing with listed building records</t>
+          <t>Description of the nature of a person's interest in the property</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -3936,7 +4072,7 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3945,105 +4081,121 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>The grade of any listed building affected by the proposed development.</t>
+          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>provided-by</t>
+          <t>interested-persons</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>informed-of-application</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Informed of application</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Source of the listed building grade information</t>
+          <t>Whether the person has been informed of the application</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>interested-persons</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>reason-not-informed</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Reason not informed</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Reason why a person was not informed of the application</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Listed building grade</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>lb-grade</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>The grade of any listed building affected by the proposed development.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>listed-building-grade</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Listed building grade</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -4054,17 +4206,17 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4073,17 +4225,17 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>The grade of any listed building affected by the proposed development.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>listed-building</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Listed building</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -4094,7 +4246,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Listed building reference for cross-referencing with listed building records</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4113,17 +4265,17 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>The grade of any listed building affected by the proposed development.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>provided-by</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Provided by</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -4134,12 +4286,12 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Source of the listed building grade information</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4149,8 +4301,16 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n"/>
-      <c r="B72" s="2" t="n"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -4158,12 +4318,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -4174,68 +4334,52 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>site-boundary</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Officer name</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -4249,36 +4393,28 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>address-text</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -4297,41 +4433,33 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Advice date</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -4345,41 +4473,33 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>easting</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Easting</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -4389,8 +4509,16 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="2" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -4408,12 +4536,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4422,17 +4550,17 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4456,31 +4584,39 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4504,26 +4640,34 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -4552,21 +4696,29 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -4600,21 +4752,29 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>usrns</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -4629,50 +4789,50 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>easting</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Easting</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4681,38 +4841,46 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>northing</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4721,33 +4889,41 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -4761,27 +4937,27 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -4790,23 +4966,31 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="2" t="n"/>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -4814,36 +4998,28 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -4862,39 +5038,215 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>contact-reference</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -4902,36 +5254,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="B73:B81"/>
-    <mergeCell ref="A43"/>
+    <mergeCell ref="B49"/>
+    <mergeCell ref="A37:A43"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A82:A87"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A50:A64"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A68:A72"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B68:B72"/>
-    <mergeCell ref="B47"/>
-    <mergeCell ref="B82:B87"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B43"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A72:A76"/>
+    <mergeCell ref="A44"/>
+    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="B45"/>
+    <mergeCell ref="B52:B68"/>
+    <mergeCell ref="B86:B91"/>
+    <mergeCell ref="A49"/>
+    <mergeCell ref="B24:B32"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="A45"/>
+    <mergeCell ref="A86:A91"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="B42"/>
-    <mergeCell ref="A73:A81"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="A69:A71"/>
+    <mergeCell ref="A77:A85"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="B44"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A52:A68"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="A42"/>
-    <mergeCell ref="A47"/>
-    <mergeCell ref="B50:B64"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="B77:B85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
